--- a/results/CB/ExperimentCBsCorrected.xlsx
+++ b/results/CB/ExperimentCBsCorrected.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G185"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,10 +460,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>SubjectNumber</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>SessionNumber</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ExperimentType</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>LogFileName</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>DataSource</t>
         </is>
@@ -491,12 +521,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>First session</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T12:49:44.174442_atom_2_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 8, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -524,12 +580,38 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Pos = Right</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T13:21:53.770221_ash_2_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 8, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -557,12 +639,38 @@
           <t>mowgli</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T14:14:41.653330_mowgli_1_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 8, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -590,12 +698,38 @@
           <t>teddy</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T14:48:40.419276_teddy_1_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 8, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -623,12 +757,38 @@
           <t>dodge</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T15:37:08.619329_dodge_1_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 8, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -656,12 +816,38 @@
           <t>filly</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT start positive at trial 9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T16:43:49.516057_filly_4_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 8, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -689,12 +875,38 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T17:27:12.851047_dougie_1_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -722,12 +934,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>53</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Positive -= RIGHT</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T18:04:47.757500_bonnie_53_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -755,12 +993,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T18:43:55.290472_apollo_1_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -788,12 +1052,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T19:32:30.778453_molly_2_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -821,12 +1111,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Experiment_2023-10-06T20:06:03.009376_bonnie_54_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -854,12 +1170,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T10:47:41.820683_atom_3_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -887,12 +1229,38 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T11:27:44.914673_ash_3_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -920,12 +1288,38 @@
           <t>mowgli</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T12:16:35.124984_mowgli_2_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -953,12 +1347,38 @@
           <t>teddy</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Positived = RIGHT</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T13:42:36.274776_teddy_2_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -986,12 +1406,38 @@
           <t>dodge</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T14:30:16.073357_dodge_2_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1019,12 +1465,38 @@
           <t>filly</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T15:21:21.434899_filly_5_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1052,12 +1524,38 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T16:13:17.750963_dougie_2_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1085,12 +1583,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>8</v>
+      </c>
+      <c r="G20" t="n">
+        <v>55</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T16:55:59.174334_bonnie_55_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1118,12 +1642,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>9</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T17:33:26.622301_apollo_2_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1151,12 +1701,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>10</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive = RIGHT  </t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Experiment_2023-10-07T18:06:05.305535_molly_3_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1184,12 +1760,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T10:29:55.247254_atom_5_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1217,12 +1819,38 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T11:03:05.275380_ash_4_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1250,12 +1878,38 @@
           <t>mowgli</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T11:48:24.989885_mowgli_3_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1283,12 +1937,38 @@
           <t>teddy</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T12:20:50.954677_teddy_3_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1316,12 +1996,38 @@
           <t>dodge</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T13:10:43.954358_dodge_3_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1349,12 +2055,38 @@
           <t>filly</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T13:50:54.095550_filly_6_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1382,12 +2114,38 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T15:37:37.287527_dougie_3_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1415,12 +2173,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" t="n">
+        <v>8</v>
+      </c>
+      <c r="G30" t="n">
+        <v>56</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Positive = RIGHT </t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T16:09:32.654028_bonnie_56_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1448,12 +2232,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>9</v>
+      </c>
+      <c r="G31" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T17:01:24.908365_apollo_3_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1481,12 +2291,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>10</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Experiment_2023-10-08T17:40:21.611860_molly_4_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1514,12 +2350,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>9</v>
+      </c>
+      <c r="G33" t="n">
+        <v>4</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T10:17:33.693352_apollo_4_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1547,12 +2409,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T11:06:00.505868_atom_6_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1580,12 +2468,38 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>5</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T11:42:20.024754_ash_5_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1613,12 +2527,38 @@
           <t>mowgli</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>4</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T12:31:10.855228_mowgli_4_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1646,12 +2586,38 @@
           <t>teddy</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T13:08:37.841616_teddy_4_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1679,12 +2645,38 @@
           <t>dodge</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T14:28:21.463730_dodge_4_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1712,12 +2704,38 @@
           <t>filly</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>6</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T15:20:02.348892_filly_8_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1745,12 +2763,38 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>7</v>
+      </c>
+      <c r="G40" t="n">
+        <v>7</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T15:25:36.471599_dougie_7_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 60, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1778,12 +2822,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>8</v>
+      </c>
+      <c r="G41" t="n">
+        <v>63</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T17:04:07.650916_bonnie_63_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 60, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1811,12 +2881,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="n">
+        <v>9</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T17:45:46.540359_apollo_5_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 60, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1844,12 +2940,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>Experiment_2023-10-09T18:34:53.096516_molly_6_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 60, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 60, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 60, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1877,12 +2999,38 @@
           <t>filly</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="n">
+        <v>6</v>
+      </c>
+      <c r="G44" t="n">
+        <v>9</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T09:46:31.020135_filly_9_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1910,12 +3058,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>7</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T10:31:23.027937_atom_7_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1943,12 +3117,38 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" t="n">
+        <v>2</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T11:11:42.463329_ash_6_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -1976,12 +3176,38 @@
           <t>mowgli</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>5</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T11:38:00.835987_mowgli_5_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2009,12 +3235,38 @@
           <t>teddy</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" t="n">
+        <v>5</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T12:20:12.178833_teddy_5_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2042,12 +3294,38 @@
           <t>dodge</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Positive =  LEFT</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T13:58:22.293380_dodge_5_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2075,12 +3353,38 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>7</v>
+      </c>
+      <c r="G50" t="n">
+        <v>8</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T16:00:54.429454_dougie_8_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2108,12 +3412,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>8</v>
+      </c>
+      <c r="G51" t="n">
+        <v>73</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T16:33:32.580268_bonnie_73_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2141,12 +3471,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>9</v>
+      </c>
+      <c r="G52" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T17:12:49.514733_apollo_6_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2174,12 +3530,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="n">
+        <v>10</v>
+      </c>
+      <c r="G53" t="n">
+        <v>7</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT Windy</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>Experiment_2023-10-10T17:48:18.431367_molly_7_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2207,12 +3589,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" t="n">
+        <v>9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>7</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>Experiment_2023-10-11T09:07:26.645788_apollo_7_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2240,12 +3648,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>Experiment_2023-10-11T09:46:53.960298_molly_8_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2273,12 +3707,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>Experiment_2023-10-11T10:26:14.965471_atom_8_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2306,12 +3766,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>9</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Positive = LEFT</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>Experiment_2023-10-12T12:02:37.453239_atom_9_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2339,12 +3825,38 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" t="n">
+        <v>2</v>
+      </c>
+      <c r="G58" t="n">
+        <v>8</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Positive + RIGHT CB T 2 after RP- A 3 criterion</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>Experiment_2023-10-16T10:39:05.806462_ash_8_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2372,12 +3884,38 @@
           <t>mowgli</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" t="n">
+        <v>3</v>
+      </c>
+      <c r="G59" t="n">
+        <v>6</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB -T 2 After RP-A 3 criterion Windy. No footage of RP-A session. </t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>Experiment_2023-10-16T11:24:59.900151_mowgli_6_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2405,12 +3943,38 @@
           <t>filly</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" t="n">
+        <v>6</v>
+      </c>
+      <c r="G60" t="n">
+        <v>10</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT, CBt 2 afer RP A 2 criterion. Leg</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>Experiment_2023-10-16T15:32:34.409339_filly_10_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2438,12 +4002,38 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" t="n">
+        <v>7</v>
+      </c>
+      <c r="G61" t="n">
+        <v>9</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Positive = RIGHT CBT 2 After RP A 32 Criterion</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>Experiment_2023-10-16T16:24:46.288311_dougie_9_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2471,12 +4061,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>CB-T 2 ater reaching cRP -A 1 criterion</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>Experiment_2023-10-17T11:03:37.586522_apollo_8_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2504,12 +4120,38 @@
           <t>teddy</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="n">
+        <v>4</v>
+      </c>
+      <c r="G63" t="n">
+        <v>6</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>CB- T 2  CB test afer RP-A 3 criterion</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>Experiment_2023-10-17T12:35:26.511897_teddy_6_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2537,12 +4179,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" t="n">
+        <v>8</v>
+      </c>
+      <c r="G64" t="n">
+        <v>77</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>CB T 2 after reaching RP-A 3 criterion</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>Experiment_2023-10-17T14:37:07.416285_bonnie_77_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2570,12 +4238,38 @@
           <t>dodge</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="n">
+        <v>5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>6</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>CB T 2, after reaching criterion in RP-A 3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>Experiment_2023-10-17T15:27:19.799243_dodge_6_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2603,12 +4297,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" t="n">
+        <v>10</v>
+      </c>
+      <c r="G66" t="n">
+        <v>9</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>CBT2 after reaching criterion RP A 2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Experiment_2023-10-17T16:49:28.592735_molly_9_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2636,12 +4356,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>10</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>CB- T 3- after reaching RP e criterion in 66 trials to five in a row</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>Experiment_2023-10-19T11:50:35.226661_atom_10_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2669,12 +4415,38 @@
           <t>atom</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" t="n">
+        <v>11</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>CB T 4 after eaching reinstatement criterion</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>Experiment_2023-10-20T10:00:38.306565_atom_11_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2702,12 +4474,38 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
+      <c r="G69" t="n">
+        <v>9</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>CB-T 3 after reaching extintion criterion</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>Experiment_2023-10-20T11:05:31.583763_ash_9_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2735,12 +4533,38 @@
           <t>mowgli</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" t="n">
+        <v>7</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>CBT-3 after reaching extiction criterion</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>Experiment_2023-10-20T11:51:36.082488_mowgli_7_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2768,12 +4592,38 @@
           <t>filly</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" t="n">
+        <v>11</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>CB T-4 after extinction RP-E criterion</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>Experiment_2023-10-20T14:08:54.608210_filly_11_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2801,12 +4651,38 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" t="n">
+        <v>7</v>
+      </c>
+      <c r="G72" t="n">
+        <v>10</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>CB-T 4 after reaching RP-E criterion</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>Experiment_2023-10-20T15:32:07.559818_dougie_10_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2834,12 +4710,38 @@
           <t>ash</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>10</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>CBTA- after reinstatement criterion reached</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>Experiment_2023-10-20T17:37:43.849099_ash_10_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2867,12 +4769,38 @@
           <t>mowgli</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>CB T -4 After reinstatement criterion</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>Experiment_2023-10-21T11:03:39.830387_mowgli_8_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2900,12 +4828,38 @@
           <t>teddy</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" t="n">
+        <v>4</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>CB T-4 after extinction criterion</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>Experiment_2023-10-21T12:03:21.675968_teddy_7_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2933,12 +4887,38 @@
           <t>dodge</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="n">
+        <v>5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>7</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>CB T-3 after extinction criterion</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>Experiment_2023-10-21T13:11:05.817830_dodge_7_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2966,12 +4946,38 @@
           <t>filly</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" t="n">
+        <v>6</v>
+      </c>
+      <c r="G77" t="n">
+        <v>12</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>CH T 4, CB-T ype 1, after reinstatement</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>Experiment_2023-10-21T14:15:00.246809_filly_12_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -2999,12 +5005,38 @@
           <t>dougie</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" t="n">
+        <v>7</v>
+      </c>
+      <c r="G78" t="n">
+        <v>11</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>CB T4, test type 1 after reinstatement</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>Experiment_2023-10-21T15:03:31.439944_dougie_11_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3032,12 +5064,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" t="n">
+        <v>8</v>
+      </c>
+      <c r="G79" t="n">
+        <v>78</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>CB T-3 after extinction</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>Experiment_2023-10-21T15:57:40.059715_bonnie_78_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3065,12 +5123,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" t="n">
+        <v>9</v>
+      </c>
+      <c r="G80" t="n">
+        <v>9</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>CB T 3, test type 3 after extinction</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>Experiment_2023-10-21T16:51:13.820180_apollo_9_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3098,12 +5182,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" t="n">
+        <v>10</v>
+      </c>
+      <c r="G81" t="n">
+        <v>10</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>CB T-3 after extinction criterion</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>Experiment_2023-10-21T17:37:08.203277_molly_10_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3131,12 +5241,38 @@
           <t>teddy</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" t="n">
+        <v>4</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP reinstatement</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>Experiment_2023-10-22T09:28:24.865198_teddy_8_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3164,12 +5300,38 @@
           <t>dodge</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP reinstatement</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>Experiment_2023-10-22T10:49:33.650259_dodge_8_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3197,12 +5359,38 @@
           <t>bonnie</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" t="n">
+        <v>8</v>
+      </c>
+      <c r="G84" t="n">
+        <v>79</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>CB -T-4 after Rp reinstatement</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>Experiment_2023-10-22T11:36:41.453331_bonnie_79_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3230,12 +5418,38 @@
           <t>apollo</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" t="n">
+        <v>9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>10</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>CB T-4 after RP- reinstatement</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>Experiment_2023-10-22T12:32:10.229170_apollo_10_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3263,12 +5477,38 @@
           <t>molly</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" t="n">
+        <v>10</v>
+      </c>
+      <c r="G86" t="n">
+        <v>11</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>CB-T 4 after RP-R reinstatement criterion</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>Experiment_2023-10-22T13:27:32.965713_molly_11_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 20, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3296,12 +5536,38 @@
           <t>george</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" t="n">
+        <v>13</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>CB-F -1</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>Experiment_2023-11-12T19:14:04.462174_george_1.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3329,12 +5595,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" t="n">
+        <v>12</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>CB F 1</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>Experiment_2023-11-12T20:44:49.282652_smudge_1.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3362,12 +5654,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" t="n">
+        <v>14</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>CB F 1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>Experiment_2023-11-12T21:26:14.605122_myrtle_1.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3395,12 +5713,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" t="n">
+        <v>16</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>CB- F 1</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>Experiment_2023-11-12T21:55:51.589728_nix_1.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3428,12 +5772,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" t="n">
+        <v>15</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>CB F 1</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>Experiment_2023-11-12T23:47:07.024641_yoshi_1.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3461,12 +5831,38 @@
           <t>gio</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" t="n">
+        <v>17</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>CB  F 1</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T00:39:24.776854_gio_1.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3494,12 +5890,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" t="n">
+        <v>18</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB F 1 </t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T01:06:46.118598_dusty_1.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3527,12 +5949,36 @@
           <t>freya</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" t="n">
+        <v>19</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>CB F 1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T01:52:41.875007_freya_nan_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3560,12 +6006,36 @@
           <t>pumba</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" t="n">
+        <v>21</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>CB F 1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T03:05:04.626964_pumba_nan_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3593,12 +6063,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" t="n">
+        <v>22</v>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>CB F 1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T04:02:49.575872_clover_nan_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3626,12 +6120,38 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" t="n">
+        <v>11</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>CB F 2</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T04:50:56.054932_jelly_2.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3659,12 +6179,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" t="n">
+        <v>12</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB F 2 Poss= Right </t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T05:23:15.688175_smudge_2.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3692,12 +6238,38 @@
           <t>george</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" t="n">
+        <v>13</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>CB F-2 Poss = LEFT</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T06:05:07.391993_george_2.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3725,12 +6297,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" t="n">
+        <v>14</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>CB F 2- Poss = RIGHT</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T06:36:50.258957_myrtle_2.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3758,12 +6356,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" t="n">
+        <v>15</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>CB F -2 Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T07:17:20.615404_yoshi_2.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3791,12 +6415,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" t="n">
+        <v>16</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>CB-F 2 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T07:47:14.435782_nix_2.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3824,12 +6474,38 @@
           <t>gio</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" t="n">
+        <v>17</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>CB F 2 Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T08:28:59.797750_gio_2.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3857,12 +6533,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F104" t="n">
+        <v>18</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>CB F 2 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T10:22:11.789817_dusty_2.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3890,12 +6592,36 @@
           <t>freya</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" t="n">
+        <v>19</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>CB F 2 Pos = lEFT</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T10:57:03.527161_freya_nan_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3923,12 +6649,36 @@
           <t>pumba</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" t="n">
+        <v>21</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>CB F 2 Poss = LEFT</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T12:06:45.400077_pumba_nan_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3956,12 +6706,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" t="n">
+        <v>22</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>CB F 2 restart at trial 5 Pos + Right</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:01:26.435669_clover_nan_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -3989,12 +6763,38 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" t="n">
+        <v>11</v>
+      </c>
+      <c r="G108" t="n">
+        <v>3</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>CB F 3- Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T13:32:28.364484_jelly_3.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4022,12 +6822,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" t="n">
+        <v>12</v>
+      </c>
+      <c r="G109" t="n">
+        <v>3</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>CB F 3 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T14:11:10.054657_smudge_3.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4055,12 +6881,38 @@
           <t>george</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" t="n">
+        <v>13</v>
+      </c>
+      <c r="G110" t="n">
+        <v>3</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>CB R 1 Pos + LEFT</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T14:49:56.787891_george_3.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4088,12 +6940,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" t="n">
+        <v>14</v>
+      </c>
+      <c r="G111" t="n">
+        <v>3</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>CB R ! Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T15:16:40.151932_myrtle_3.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4121,12 +6999,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" t="n">
+        <v>15</v>
+      </c>
+      <c r="G112" t="n">
+        <v>3</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>CB R 1 Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T16:03:04.381618_yoshi_3.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4154,12 +7058,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" t="n">
+        <v>16</v>
+      </c>
+      <c r="G113" t="n">
+        <v>3</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB R 1 Pos = RIGHT </t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T16:34:23.409480_nix_3.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4187,12 +7117,38 @@
           <t>gio</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" t="n">
+        <v>17</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>CB R 1 Pos + LEFT</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T17:24:29.152222_gio_3.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4220,12 +7176,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" t="n">
+        <v>18</v>
+      </c>
+      <c r="G115" t="n">
+        <v>3</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>CB R 1 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T18:03:46.698927_dusty_3.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4253,12 +7235,36 @@
           <t>freya</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" t="n">
+        <v>19</v>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB R 1 Poss = LEFT  </t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T19:19:51.364628_freya_nan_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4286,12 +7292,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" t="n">
+        <v>22</v>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>CB R 1  Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T20:49:33.970464_clover_nan_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4319,12 +7349,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" t="n">
+        <v>22</v>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>CB  R 1 second file Pos = R</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T20:54:16.427672_clover_nan_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4352,12 +7406,36 @@
           <t>pumba</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" t="n">
+        <v>21</v>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>CB F 3 Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T21:26:18.412625_pumba_nan_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4385,12 +7463,38 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" t="n">
+        <v>11</v>
+      </c>
+      <c r="G120" t="n">
+        <v>4</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Training - fixed</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>CB F 4 Pos =LEft</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T23:02:01.120208_jelly_4.0_Training - fixed.log</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4418,12 +7522,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" t="n">
+        <v>12</v>
+      </c>
+      <c r="G121" t="n">
+        <v>4</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>CB R 3 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>Experiment_2023-11-13T23:31:59.936909_smudge_4.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4451,12 +7581,38 @@
           <t>george</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" t="n">
+        <v>13</v>
+      </c>
+      <c r="G122" t="n">
+        <v>5</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>CB T 1 Pos + LEFT</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T00:25:42.956340_george_5.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4484,12 +7640,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" t="n">
+        <v>14</v>
+      </c>
+      <c r="G123" t="n">
+        <v>4</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>CB R 2 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T00:45:14.508317_myrtle_4.0_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4517,12 +7699,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" t="n">
+        <v>14</v>
+      </c>
+      <c r="G124" t="n">
+        <v>5</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>end of previous session</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T01:18:45.941991_myrtle_5.0_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4550,12 +7758,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" t="n">
+        <v>15</v>
+      </c>
+      <c r="G125" t="n">
+        <v>4</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Cb R 1 Pos =LEFT</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T01:55:54.666841_yoshi_4.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4583,12 +7817,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" t="n">
+        <v>16</v>
+      </c>
+      <c r="G126" t="n">
+        <v>4</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Cb T 1 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T02:26:16.452913_nix_4.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4616,12 +7876,38 @@
           <t>gio</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" t="n">
+        <v>17</v>
+      </c>
+      <c r="G127" t="n">
+        <v>4</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>CB R 2 Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:07:06.316598_gio_4.0_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4649,12 +7935,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" t="n">
+        <v>18</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB R 2 Poss = LEFT </t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T04:38:56.660845_dusty_4.0_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4682,12 +7994,36 @@
           <t>freya</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" t="n">
+        <v>19</v>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>CB T 1 Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T05:29:24.069610_freya_nan_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4715,12 +8051,36 @@
           <t>pumba</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" t="n">
+        <v>21</v>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB T 1 Poss = LEFT  </t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T06:35:09.308410_pumba_nan_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4748,12 +8108,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" t="n">
+        <v>22</v>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>CB R 2 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T07:17:26.885747_clover_nan_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4781,12 +8165,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" t="n">
+        <v>16</v>
+      </c>
+      <c r="G132" t="n">
+        <v>5</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Cb R 2 after CBT wrongly given Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T08:02:44.063274_nix_5.0_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4814,12 +8224,38 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" t="n">
+        <v>11</v>
+      </c>
+      <c r="G133" t="n">
+        <v>5</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>CB R 1 Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T08:46:04.505826_jelly_5.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4847,12 +8283,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" t="n">
+        <v>12</v>
+      </c>
+      <c r="G134" t="n">
+        <v>5</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>CB R 2 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T09:21:32.260775_smudge_5.0_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4880,12 +8342,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" t="n">
+        <v>14</v>
+      </c>
+      <c r="G135" t="n">
+        <v>6</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>CB r 3 Poss = RIGHT</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T10:23:47.643202_myrtle_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4913,12 +8401,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F136" t="n">
+        <v>16</v>
+      </c>
+      <c r="G136" t="n">
+        <v>7</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>CB R 3 Poss = RIGHT</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T11:07:04.244882_nix_7.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4946,12 +8460,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" t="n">
+        <v>15</v>
+      </c>
+      <c r="G137" t="n">
+        <v>5</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>CB R 2 Poss = LEFT</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T11:34:20.820883_yoshi_5.0_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -4979,12 +8519,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" t="n">
+        <v>18</v>
+      </c>
+      <c r="G138" t="n">
+        <v>6</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>CB R 3 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T12:13:40.543722_dusty_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5012,12 +8578,38 @@
           <t>gio</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" t="n">
+        <v>17</v>
+      </c>
+      <c r="G139" t="n">
+        <v>5</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB T1 pos = LEFT Windy/hot </t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T12:37:30.469954_gio_5.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5045,12 +8637,36 @@
           <t>pumba</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F140" t="n">
+        <v>21</v>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Training randomised Type 2</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Cb R 2 Pos = LEFT hot/windy</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T15:40:26.284336_pumba_nan_Training randomised Type 2.log</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5078,12 +8694,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F141" t="n">
+        <v>22</v>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Cb T 1 Poss = LEFT</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T16:29:57.013745_clover_nan_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5111,12 +8751,38 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F142" t="n">
+        <v>11</v>
+      </c>
+      <c r="G142" t="n">
+        <v>6</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>CB T 1 Poss = LEFT windy</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T17:14:25.139579_jelly_6.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5144,12 +8810,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" t="n">
+        <v>12</v>
+      </c>
+      <c r="G143" t="n">
+        <v>6</v>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>CB R 3 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T17:33:48.603698_smudge_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5177,12 +8869,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" t="n">
+        <v>14</v>
+      </c>
+      <c r="G144" t="n">
+        <v>8</v>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>CB T 1 restart test</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T18:48:28.476282_myrtle_8.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5210,12 +8928,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" t="n">
+        <v>15</v>
+      </c>
+      <c r="G145" t="n">
+        <v>6</v>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Training randomised Type 1</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>CB R 3 Poss =LEFT</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T19:16:58.918521_yoshi_6.0_Training randomised Type 1.log</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5243,12 +8987,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F146" t="n">
+        <v>16</v>
+      </c>
+      <c r="G146" t="n">
+        <v>8</v>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>CB T 1 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T19:42:46.106423_nix_8.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5276,12 +9046,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F147" t="n">
+        <v>18</v>
+      </c>
+      <c r="G147" t="n">
+        <v>7</v>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>CB T 1 Pos = RIGHT</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T20:37:30.423056_dusty_7.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5309,12 +9105,36 @@
           <t>freya</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F148" t="n">
+        <v>19</v>
+      </c>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>CB T 2 after RP A criterion v wi dy, rain</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>Experiment_2023-11-14T23:17:57.967289_freya_nan_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5342,12 +9162,36 @@
           <t>pumba</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F149" t="n">
+        <v>21</v>
+      </c>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>CB T 1 Pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T00:06:05.447953_pumba_nan_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5375,12 +9219,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" t="n">
+        <v>22</v>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>CB T 1 poss = RIGHT</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T00:39:50.244185_clover_nan_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5408,12 +9276,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F151" t="n">
+        <v>12</v>
+      </c>
+      <c r="G151" t="n">
+        <v>7</v>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>CB T 1 Poss = RIGHT</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T02:11:18.965110_smudge_7.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5441,12 +9335,38 @@
           <t>george</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F152" t="n">
+        <v>13</v>
+      </c>
+      <c r="G152" t="n">
+        <v>6</v>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>CB T 2 after RP A 3 acquisition pos = LEFT</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T02:59:50.231712_george_6.0_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5474,12 +9394,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F153" t="n">
+        <v>15</v>
+      </c>
+      <c r="G153" t="n">
+        <v>8</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>CB T 1 Poss = LEFT</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T03:51:22.577702_yoshi_8.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5507,12 +9453,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F154" t="n">
+        <v>16</v>
+      </c>
+      <c r="G154" t="n">
+        <v>9</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>CB T 2 after RP A 1 acquisition Poss = LEFT</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T04:42:42.109160_nix_9.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5540,12 +9512,38 @@
           <t>gio</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F155" t="n">
+        <v>17</v>
+      </c>
+      <c r="G155" t="n">
+        <v>6</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>CB T 2 after RPA 2 aquitisiton</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T05:22:53.513691_gio_6.0_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5573,12 +9571,38 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
+      <c r="F156" t="n">
+        <v>11</v>
+      </c>
+      <c r="G156" t="n">
+        <v>7</v>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>CBT 2 after RP A 4 acquisition</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T16:04:18.871968_jelly_7.0_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5606,12 +9630,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F157" t="n">
+        <v>12</v>
+      </c>
+      <c r="G157" t="n">
+        <v>8</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB T 2 after acquisition RP A 4 </t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T16:42:36.211643_smudge_8.0_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5639,12 +9689,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F158" t="n">
+        <v>14</v>
+      </c>
+      <c r="G158" t="n">
+        <v>9</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>CBT 2 after RP A 3 acquisition</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T17:59:06.826933_myrtle_9.0_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5672,12 +9748,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F159" t="n">
+        <v>15</v>
+      </c>
+      <c r="G159" t="n">
+        <v>9</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>CB T 2 after RP A 2 acquisition</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T18:35:59.371714_yoshi_9.0_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5705,12 +9807,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F160" t="n">
+        <v>18</v>
+      </c>
+      <c r="G160" t="n">
+        <v>8</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>CB T 2 after RP A 3 acquisition</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T20:13:26.521959_dusty_8.0_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5738,12 +9866,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F161" t="n">
+        <v>22</v>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>CB T 2 after RP A 3 acqusition criterion</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>Experiment_2023-11-15T23:18:27.463685_clover_nan_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5771,12 +9923,36 @@
           <t>pumba</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F162" t="n">
+        <v>21</v>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Test Type 2</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>CB T 2 after RP A 4 acquisition criterion</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T00:37:29.832581_pumba_nan_Test Type 2.log</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5804,12 +9980,36 @@
           <t>freya</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F163" t="n">
+        <v>19</v>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Cb T 3 aftter RP E raining</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T05:15:17.737341_freya_nan_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5837,12 +10037,38 @@
           <t>george</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F164" t="n">
+        <v>13</v>
+      </c>
+      <c r="G164" t="n">
+        <v>7</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>CB T 3 after RP E acquisition</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T07:57:12.097353_george_7.0_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5870,12 +10096,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
+      <c r="F165" t="n">
+        <v>16</v>
+      </c>
+      <c r="G165" t="n">
+        <v>10</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CBT 3 after RP E </t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:12:31.465402_nix_10.0_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5903,12 +10155,38 @@
           <t>gio</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F166" t="n">
+        <v>17</v>
+      </c>
+      <c r="G166" t="n">
+        <v>7</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>CB T 3 after RP E</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T09:54:53.813828_gio_7.0_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5936,12 +10214,36 @@
           <t>freya</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F167" t="n">
+        <v>19</v>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T11:37:18.984569_freya_nan_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -5969,12 +10271,38 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F168" t="n">
+        <v>11</v>
+      </c>
+      <c r="G168" t="n">
+        <v>8</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>CB T 3 after RP E arena is slippery</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T13:01:14.550048_jelly_8.0_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6002,12 +10330,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F169" t="n">
+        <v>12</v>
+      </c>
+      <c r="G169" t="n">
+        <v>9</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB T 3 after RP E </t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T13:46:25.228604_smudge_9.0_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6035,12 +10389,38 @@
           <t>george</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F170" t="n">
+        <v>13</v>
+      </c>
+      <c r="G170" t="n">
+        <v>8</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T14:31:05.230974_george_8.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6068,12 +10448,38 @@
           <t>nix</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F171" t="n">
+        <v>16</v>
+      </c>
+      <c r="G171" t="n">
+        <v>11</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T15:46:42.899255_nix_11.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6101,12 +10507,38 @@
           <t>gio</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F172" t="n">
+        <v>17</v>
+      </c>
+      <c r="G172" t="n">
+        <v>9</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R second file</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T17:55:24.333022_gio_9.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6134,12 +10566,38 @@
           <t>jelly</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F173" t="n">
+        <v>11</v>
+      </c>
+      <c r="G173" t="n">
+        <v>9</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T19:24:59.492473_jelly_9.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6167,12 +10625,38 @@
           <t>smudge</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F174" t="n">
+        <v>12</v>
+      </c>
+      <c r="G174" t="n">
+        <v>10</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>CBT 4 after RP E = two RP ER sessions</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T20:27:00.214523_smudge_10.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6200,12 +10684,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F175" t="n">
+        <v>14</v>
+      </c>
+      <c r="G175" t="n">
+        <v>10</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB T 3 after RP E </t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T21:17:46.006067_myrtle_10.0_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6233,12 +10743,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
+      <c r="F176" t="n">
+        <v>15</v>
+      </c>
+      <c r="G176" t="n">
+        <v>10</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>CB T 3 after RP E</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T22:01:25.798273_yoshi_10.0_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6266,12 +10802,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
+      <c r="F177" t="n">
+        <v>18</v>
+      </c>
+      <c r="G177" t="n">
+        <v>9</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CB T 3 after RP E </t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
         <is>
           <t>Experiment_2023-11-16T23:55:33.357304_dusty_9.0_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6299,12 +10861,36 @@
           <t>pumba</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
+      <c r="F178" t="n">
+        <v>21</v>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>CB T 3 after RP E</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T00:36:27.593791_pumba_nan_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6332,12 +10918,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
+      <c r="F179" t="n">
+        <v>22</v>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Test Type 3</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>CB T 3 after RP E</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T01:23:36.375164_clover_nan_Test Type 3.log</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6365,12 +10975,38 @@
           <t>myrtle</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F180" t="n">
+        <v>14</v>
+      </c>
+      <c r="G180" t="n">
+        <v>11</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T02:45:25.056724_myrtle_11.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6398,12 +11034,38 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
+      <c r="F181" t="n">
+        <v>15</v>
+      </c>
+      <c r="G181" t="n">
+        <v>11</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>LEFT</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T03:22:54.109367_yoshi_11.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6431,12 +11093,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
+      <c r="F182" t="n">
+        <v>18</v>
+      </c>
+      <c r="G182" t="n">
+        <v>10</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:05:53.213724_dusty_10.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6464,12 +11152,38 @@
           <t>dusty</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
+      <c r="F183" t="n">
+        <v>18</v>
+      </c>
+      <c r="G183" t="n">
+        <v>11</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>CBT 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T04:39:51.602365_dusty_11.0_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6497,12 +11211,36 @@
           <t>clover</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
+      <c r="F184" t="n">
+        <v>22</v>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Test Type 1</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>RIGHT</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>CB T 4 after RP R</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
         <is>
           <t>Experiment_2023-11-17T05:22:49.445377_clover_nan_Test Type 1.log</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>{"CRITERION_TIMEOUT_TRAINING": 20, "FEED_DISPENSE": 20, "FIRST_TRIAL_DURATION": 4, "INITIAL_DELAY": 10, "MAX_TIME_START_TO_TOUCH_EVENT": 300, "MAX_TRIAL_PER_SESSION": 20, "MODE": "test", "NEGATIVE_RESPONSE_TIMEOUT": 30, "N_SUBJECT": 30, "N_TOUCH": 3, "PAUSE_BETWEEN_TRIALS": 5, "POSITIVE_RESPONSE_TIMEOUT": 30, "SENSITIVITY": 5, "SERVO_CHANNEL": 1, "SERVO_CLOSE": 0, "SERVO_DELAY": 0.7, "SERVO_DELAY_AFTER_FEED": 3, "SERVO_MODE": "pellets", "SERVO_OPEN": 180, "SESSION_STARTED_SOUND_DURATION": 2, "SESSION_TERMINATED_SOUND_DURATION": 2, "SYSTEM_READY_SOUND_DURATION": 2, "TEST_TIMEOUT": 30, "TOUCH_PAD_DELAY": 0.1, "TRIAL_LIMIT": 20, "TRIAL_SLEEP_TIME": 5, "TRIAL_SOUND_DURATION": 1}</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
         <is>
           <t>ExperimentCBs</t>
         </is>
@@ -6530,12 +11268,22 @@
           <t>yoshi</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Ran CBR1 but should be CBF3- so manually check all timings</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
         <is>
           <t>NO_LOGFILE_AVAILABLE_CSU_2023-11-17_CBF3_yoshi</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
         <is>
           <t>Corrections xlsx: ADD</t>
         </is>
